--- a/11-management/project-phase-progress.xlsx
+++ b/11-management/project-phase-progress.xlsx
@@ -1271,7 +1271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="53.5555555555556" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col width="8.77777777777778" customWidth="1" style="1" min="1" max="1"/>
@@ -1482,6 +1482,73 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P2-1 依赖清理+阻塞BUG修复</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已完成（2026-09-19）</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OpenCV 收敛为 2 包（4.10.0.84 同版本）；pynvml 21ms 替换 nvidia-smi 147ms；BUG-1 区域截图 / BUG-3 OCR 常驻已修并实跑验证</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>56 单测全绿；区域截图 [320,200]；OCR 冷启 8888ms / 推理 106ms</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BUG-2 / BUG-4 移交 P2-2 收尾</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P2-2 七层目录骨架（方案B迁移）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>基本完成（暂停中）</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P2-layers/contracts 9 文件 + env_adapter 7 文件已迁；P1 侧留 shim；基线 c66e5d9 已推远端</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>56 单测 OK（0.413s）；16 文件行数与迁移前逐一比对一致</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>收尾 5 项：#1 改调用方 import；#2 删 shim；#3 P1 目录改名；#4 feature flag；#5 BUG-2+BUG-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—— 2026-09-19 18:4x 更新：追加第 9/10 两行；进度细则以 11-management/接下来的任务.txt（10 轮制）为准 ——</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
